--- a/examples/ExamplesFromPaper/BondCleavage/Hetero1.rkf.xlsx
+++ b/examples/ExamplesFromPaper/BondCleavage/Hetero1.rkf.xlsx
@@ -26,13 +26,13 @@
     <sheet name="Contr F" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'FMOs CH3'!$B$3:$L$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FMOs F'!$B$3:$L$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOs!$B$3:$J$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rᴼᴵ (appr.)'!$B$3:$R$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rᴼᴵ (eff.)'!$B$3:$R$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rᴼᴵ (reg.)'!$B$3:$R$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rᴾᴿ!$B$3:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'FMOs CH3'!$B$5:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FMOs F'!$B$5:$L$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOs!$B$5:$J$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Rᴼᴵ (appr.)'!$B$5:$R$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rᴼᴵ (eff.)'!$B$5:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rᴼᴵ (reg.)'!$B$5:$R$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rᴾᴿ!$B$5:$O$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66047,7 +66047,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R49"/>
+  <autoFilter ref="B5:R49"/>
   <dataValidations count="17">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -68807,7 +68807,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R52"/>
+  <autoFilter ref="B5:R52"/>
   <dataValidations count="17">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -71514,7 +71514,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:R51"/>
+  <autoFilter ref="B5:R51"/>
   <dataValidations count="17">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -72005,7 +72005,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:O11"/>
+  <autoFilter ref="B5:O11"/>
   <dataValidations count="14">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="ψᵢ" prompt="Fragment molecular orbital ψᵢ." sqref="B5"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="oᵢ" prompt="Initial occupation of FMO ψᵢ." sqref="C5"/>
@@ -74550,7 +74550,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:J87"/>
+  <autoFilter ref="B5:J87"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -76687,7 +76687,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:L61"/>
+  <autoFilter ref="B5:L61"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -77669,7 +77669,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:L28"/>
+  <autoFilter ref="B5:L28"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
